--- a/artfynd/A 7447-2024 artfynd.xlsx
+++ b/artfynd/A 7447-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117103771</v>
       </c>
       <c r="B2" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117105330</v>
+        <v>117103792</v>
       </c>
       <c r="B3" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323560</v>
+        <v>323574</v>
       </c>
       <c r="R3" t="n">
-        <v>6591927</v>
+        <v>6591921</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -902,6 +892,336 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117105273</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väst. Uppsalstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>323582</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6591982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Holmedal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spelspillning på sliten mark</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117105303</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väst. Uppsalstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>323574</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6591974</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Holmedal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spelspillning på sliten mark</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117105330</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Väst. Uppsalstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>323560</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6591927</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Holmedal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spelspillning på sliten mark</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
